--- a/output/Пересбор_прайсов_v2_отчёт_2026-09-23.xlsx
+++ b/output/Пересбор_прайсов_v2_отчёт_2026-09-23.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>388401</v>
+        <v>387037</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="6">
@@ -1638,11 +1638,11 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>{"позиций": 7, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 45, "дубли": 0.0, "мед. доля": 0.86}</t>
+          <t>{"позиций": 6, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 44.5, "дубли": 0.0, "мед. доля": 0.83}</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1823,11 +1823,11 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>{"позиций": 95, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 38, "дубли": 0.0, "мед. доля": 0.47}</t>
+          <t>{"позиций": 94, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 38.0, "дубли": 0.0, "мед. доля": 0.47}</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -2588,11 +2588,11 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>{"позиций": 97, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 31, "дубли": 0.11, "мед. доля": 0.87}</t>
+          <t>{"позиций": 91, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 31, "дубли": 0.08, "мед. доля": 0.86}</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2798,11 +2798,11 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>{"позиций": 174, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 22.5, "дубли": 0.05, "мед. доля": 0.49}</t>
+          <t>{"позиций": 173, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 22, "дубли": 0.05, "мед. доля": 0.49}</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -3668,11 +3668,11 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>2279</v>
+        <v>2277</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>{"позиций": 2279, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 54, "дубли": 0.04, "мед. доля": 0.53}</t>
+          <t>{"позиций": 2277, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 54, "дубли": 0.04, "мед. доля": 0.53}</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -4143,11 +4143,11 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>{"позиций": 479, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 56, "дубли": 0.08, "мед. доля": 0.59}</t>
+          <t>{"позиций": 471, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 56, "дубли": 0.08, "мед. доля": 0.59}</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -4476,11 +4476,11 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>{"позиций": 83, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 60, "дубли": 0.0, "мед. доля": 0.87}</t>
+          <t>{"позиций": 75, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 54, "дубли": 0.0, "мед. доля": 0.85}</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -5460,11 +5460,11 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>{"позиций": 23, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 29, "дубли": 0.22, "мед. доля": 0.52}</t>
+          <t>{"позиций": 22, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 24.5, "дубли": 0.23, "мед. доля": 0.5}</t>
         </is>
       </c>
       <c r="F136" t="n">
@@ -6068,11 +6068,11 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>2593</v>
+        <v>2549</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>{"позиций": 2593, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 40, "дубли": 0.03, "мед. доля": 0.41}</t>
+          <t>{"позиций": 2549, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 40, "дубли": 0.02, "мед. доля": 0.41}</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -6139,11 +6139,11 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>2338</v>
+        <v>2336</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>{"позиций": 2338, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 42.0, "дубли": 0.01, "мед. доля": 0.55}</t>
+          <t>{"позиций": 2336, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 42.0, "дубли": 0.01, "мед. доля": 0.55}</t>
         </is>
       </c>
       <c r="F155" t="n">
@@ -6287,11 +6287,11 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>{"позиций": 250, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 52.0, "дубли": 0.04, "мед. доля": 0.79}</t>
+          <t>{"позиций": 248, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 52.0, "дубли": 0.04, "мед. доля": 0.79}</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -6830,11 +6830,11 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>{"позиций": 344, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 103.0, "дубли": 0.03, "мед. доля": 0.75}</t>
+          <t>{"позиций": 343, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 103, "дубли": 0.03, "мед. доля": 0.75}</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -7364,11 +7364,11 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>{"позиций": 246, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 66.5, "дубли": 0.02, "мед. доля": 0.76}</t>
+          <t>{"позиций": 243, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 68, "дубли": 0.02, "мед. доля": 0.76}</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -8040,11 +8040,11 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>{"позиций": 292, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 47.0, "дубли": 0.01, "мед. доля": 0.92}</t>
+          <t>{"позиций": 288, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 47.0, "дубли": 0.01, "мед. доля": 0.92}</t>
         </is>
       </c>
       <c r="F208" t="n">
@@ -8941,11 +8941,11 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>{"позиций": 1554, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 38.0, "дубли": 0.02, "мед. доля": 0.59}</t>
+          <t>{"позиций": 1553, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 38, "дубли": 0.02, "мед. доля": 0.59}</t>
         </is>
       </c>
       <c r="F233" t="n">
@@ -9231,11 +9231,11 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>1054</v>
+        <v>1037</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>{"позиций": 1054, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 49.0, "дубли": 0.0, "мед. доля": 0.55}</t>
+          <t>{"позиций": 1037, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 49, "дубли": 0.0, "мед. доля": 0.54}</t>
         </is>
       </c>
       <c r="F241" t="n">
@@ -9734,11 +9734,11 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>514</v>
+        <v>497</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>{"позиций": 514, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 47.0, "дубли": 0.03, "мед. доля": 0.77}</t>
+          <t>{"позиций": 497, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 47, "дубли": 0.03, "мед. доля": 0.77}</t>
         </is>
       </c>
       <c r="F255" t="n">
@@ -10101,11 +10101,11 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>727</v>
+        <v>714</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>{"позиций": 727, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 82, "дубли": 0.05, "мед. доля": 0.89}</t>
+          <t>{"позиций": 714, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 82.0, "дубли": 0.05, "мед. доля": 0.89}</t>
         </is>
       </c>
       <c r="F265" t="n">
@@ -10641,11 +10641,11 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>{"позиций": 1030, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 53.0, "дубли": 0.21, "мед. доля": 0.58}</t>
+          <t>{"позиций": 1020, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 53.0, "дубли": 0.21, "мед. доля": 0.59}</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -10897,11 +10897,11 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>7557</v>
+        <v>7533</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>{"позиций": 7557, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 93, "дубли": 0.01, "мед. доля": 0.38}</t>
+          <t>{"позиций": 7533, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 93, "дубли": 0.01, "мед. доля": 0.38}</t>
         </is>
       </c>
       <c r="F287" t="n">
@@ -12230,11 +12230,11 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>{"позиций": 245, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 44, "дубли": 0.15, "мед. доля": 0.74}</t>
+          <t>{"позиций": 244, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 44.0, "дубли": 0.15, "мед. доля": 0.74}</t>
         </is>
       </c>
       <c r="F324" t="n">
@@ -12835,11 +12835,11 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>{"позиций": 1032, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 39.0, "дубли": 0.02, "мед. доля": 0.51}</t>
+          <t>{"позиций": 1031, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 39, "дубли": 0.02, "мед. доля": 0.51}</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -13662,11 +13662,11 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>{"позиций": 1847, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 37, "дубли": 0.03, "мед. доля": 0.43}</t>
+          <t>{"позиций": 1846, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 37.0, "дубли": 0.03, "мед. доля": 0.43}</t>
         </is>
       </c>
       <c r="F364" t="n">
@@ -14813,11 +14813,11 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>3016</v>
+        <v>3013</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>{"позиций": 3016, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 59.0, "дубли": 0.0, "мед. доля": 0.62}</t>
+          <t>{"позиций": 3013, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 59, "дубли": 0.0, "мед. доля": 0.62}</t>
         </is>
       </c>
       <c r="F396" t="n">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>{"позиций": 4, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 95.5, "дубли": 0.0, "мед. доля": 0.5}</t>
+          <t>{"позиций": 0}</t>
         </is>
       </c>
       <c r="F398" t="n">
@@ -14924,11 +14924,11 @@
         </is>
       </c>
       <c r="D399" t="n">
-        <v>434</v>
+        <v>418</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>{"позиций": 434, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 47.0, "дубли": 0.04, "мед. доля": 0.63}</t>
+          <t>{"позиций": 418, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 47.0, "дубли": 0.04, "мед. доля": 0.62}</t>
         </is>
       </c>
       <c r="F399" t="n">
@@ -15242,11 +15242,11 @@
         </is>
       </c>
       <c r="D408" t="n">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>{"позиций": 1149, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 39, "дубли": 0.0, "мед. доля": 0.39}</t>
+          <t>{"позиций": 1147, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 39, "дубли": 0.0, "мед. доля": 0.39}</t>
         </is>
       </c>
       <c r="F408" t="n">
@@ -15462,7 +15462,7 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>{"позиций": 185, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 20, "дубли": 0.14, "мед. доля": 0.0}</t>
+          <t>{"позиций": 184, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 20.5, "дубли": 0.14, "мед. доля": 0.0}</t>
         </is>
       </c>
       <c r="F414" t="n">
@@ -15640,11 +15640,11 @@
         </is>
       </c>
       <c r="D419" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>{"позиций": 18, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 35.5, "дубли": 0.0, "мед. доля": 0.83}</t>
+          <t>{"позиций": 16, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 31.0, "дубли": 0.0, "мед. доля": 0.81}</t>
         </is>
       </c>
       <c r="F419" t="n">
@@ -15924,11 +15924,11 @@
         </is>
       </c>
       <c r="D427" t="n">
-        <v>1676</v>
+        <v>1673</v>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>{"позиций": 1676, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 78.0, "дубли": 0.0, "мед. доля": 0.52}</t>
+          <t>{"позиций": 1673, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 78, "дубли": 0.0, "мед. доля": 0.52}</t>
         </is>
       </c>
       <c r="F427" t="n">
@@ -16106,11 +16106,11 @@
         </is>
       </c>
       <c r="D432" t="n">
-        <v>1211</v>
+        <v>1142</v>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>{"позиций": 1211, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 58, "дубли": 0.01, "мед. доля": 0.57}</t>
+          <t>{"позиций": 1142, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 55.0, "дубли": 0.01, "мед. доля": 0.54}</t>
         </is>
       </c>
       <c r="F432" t="n">
@@ -16322,11 +16322,11 @@
         </is>
       </c>
       <c r="D438" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>{"позиций": 30, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 71.0, "дубли": 0.03, "мед. доля": 0.7}</t>
+          <t>{"позиций": 27, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 73, "дубли": 0.0, "мед. доля": 0.7}</t>
         </is>
       </c>
       <c r="F438" t="n">
@@ -16572,11 +16572,11 @@
         </is>
       </c>
       <c r="D445" t="n">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>{"позиций": 107, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 56, "дубли": 0.01, "мед. доля": 0.66}</t>
+          <t>{"позиций": 100, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 54.5, "дубли": 0.0, "мед. доля": 0.65}</t>
         </is>
       </c>
       <c r="F445" t="n">
@@ -16754,11 +16754,11 @@
         </is>
       </c>
       <c r="D450" t="n">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>{"позиций": 240, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 63.0, "дубли": 0.05, "мед. доля": 0.74}</t>
+          <t>{"позиций": 238, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 46.0, "дубли": 0.05, "мед. доля": 0.74}</t>
         </is>
       </c>
       <c r="F450" t="n">
@@ -16791,11 +16791,11 @@
         </is>
       </c>
       <c r="D451" t="n">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>{"позиций": 95, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 54, "дубли": 0.0, "мед. доля": 0.74}</t>
+          <t>{"позиций": 84, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 54.0, "дубли": 0.0, "мед. доля": 0.74}</t>
         </is>
       </c>
       <c r="F451" t="n">
@@ -17121,11 +17121,11 @@
         </is>
       </c>
       <c r="D460" t="n">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>{"позиций": 305, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 31, "дубли": 0.0, "мед. доля": 0.6}</t>
+          <t>{"позиций": 303, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 31, "дубли": 0.0, "мед. доля": 0.6}</t>
         </is>
       </c>
       <c r="F460" t="n">
@@ -17300,11 +17300,11 @@
         </is>
       </c>
       <c r="D465" t="n">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>{"позиций": 843, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 43, "дубли": 0.0, "мед. доля": 0.52}</t>
+          <t>{"позиций": 840, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 43.0, "дубли": 0.0, "мед. доля": 0.52}</t>
         </is>
       </c>
       <c r="F465" t="n">
@@ -18207,11 +18207,11 @@
         </is>
       </c>
       <c r="D490" t="n">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>{"позиций": 576, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 45.0, "дубли": 0.09, "мед. доля": 0.76}</t>
+          <t>{"позиций": 574, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 45.0, "дубли": 0.08, "мед. доля": 0.76}</t>
         </is>
       </c>
       <c r="F490" t="n">
@@ -18862,7 +18862,7 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>{"позиций": 4, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 96.0, "дубли": 0.0, "мед. доля": 0.75}</t>
+          <t>{"позиций": 3, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 84, "дубли": 0.0, "мед. доля": 0.67}</t>
         </is>
       </c>
       <c r="F508" t="n">
@@ -19262,11 +19262,11 @@
         </is>
       </c>
       <c r="D519" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>{"позиций": 378, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 53.0, "дубли": 0.03, "мед. доля": 0.79}</t>
+          <t>{"позиций": 377, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 53, "дубли": 0.03, "мед. доля": 0.79}</t>
         </is>
       </c>
       <c r="F519" t="n">
@@ -20879,11 +20879,11 @@
         </is>
       </c>
       <c r="D564" t="n">
-        <v>583</v>
+        <v>472</v>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>{"позиций": 583, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 76, "дубли": 0.01, "мед. доля": 0.74}</t>
+          <t>{"позиций": 472, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 69.0, "дубли": 0.01, "мед. доля": 0.7}</t>
         </is>
       </c>
       <c r="F564" t="n">
@@ -20950,11 +20950,11 @@
         </is>
       </c>
       <c r="D566" t="n">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>{"позиций": 244, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 55.0, "дубли": 0.01, "мед. доля": 0.76}</t>
+          <t>{"позиций": 228, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 54.0, "дубли": 0.01, "мед. доля": 0.75}</t>
         </is>
       </c>
       <c r="F566" t="n">
@@ -21422,11 +21422,11 @@
         </is>
       </c>
       <c r="D579" t="n">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>{"позиций": 147, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 28, "дубли": 0.04, "мед. доля": 0.7}</t>
+          <t>{"позиций": 142, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 28.0, "дубли": 0.01, "мед. доля": 0.69}</t>
         </is>
       </c>
       <c r="F579" t="n">
@@ -22255,11 +22255,11 @@
         </is>
       </c>
       <c r="D602" t="n">
-        <v>679</v>
+        <v>670</v>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>{"позиций": 679, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 48, "дубли": 0.01, "мед. доля": 0.59}</t>
+          <t>{"позиций": 670, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 48.0, "дубли": 0.0, "мед. доля": 0.6}</t>
         </is>
       </c>
       <c r="F602" t="n">
@@ -22400,11 +22400,11 @@
         </is>
       </c>
       <c r="D606" t="n">
-        <v>973</v>
+        <v>957</v>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>{"позиций": 973, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 44, "дубли": 0.09, "мед. доля": 0.52}</t>
+          <t>{"позиций": 957, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 44, "дубли": 0.09, "мед. доля": 0.53}</t>
         </is>
       </c>
       <c r="F606" t="n">
@@ -22545,11 +22545,11 @@
         </is>
       </c>
       <c r="D610" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>{"позиций": 167, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 35, "дубли": 0.17, "мед. доля": 0.8}</t>
+          <t>{"позиций": 165, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 35, "дубли": 0.18, "мед. доля": 0.79}</t>
         </is>
       </c>
       <c r="F610" t="n">
@@ -22798,11 +22798,11 @@
         </is>
       </c>
       <c r="D617" t="n">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>{"позиций": 155, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 35, "дубли": 0.17, "мед. доля": 0.93}</t>
+          <t>{"позиций": 143, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 36, "дубли": 0.12, "мед. доля": 0.92}</t>
         </is>
       </c>
       <c r="F617" t="n">
@@ -23014,11 +23014,11 @@
         </is>
       </c>
       <c r="D623" t="n">
-        <v>1651</v>
+        <v>1644</v>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>{"позиций": 1651, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 37, "дубли": 0.02, "мед. доля": 0.61}</t>
+          <t>{"позиций": 1644, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 37.0, "дубли": 0.02, "мед. доля": 0.6}</t>
         </is>
       </c>
       <c r="F623" t="n">
@@ -23270,11 +23270,11 @@
         </is>
       </c>
       <c r="D630" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>{"позиций": 223, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 90, "дубли": 0.06, "мед. доля": 0.69}</t>
+          <t>{"позиций": 220, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 87.5, "дубли": 0.06, "мед. доля": 0.7}</t>
         </is>
       </c>
       <c r="F630" t="n">
@@ -23529,11 +23529,11 @@
         </is>
       </c>
       <c r="D637" t="n">
-        <v>2777</v>
+        <v>2775</v>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>{"позиций": 2777, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 56, "дубли": 0.05, "мед. доля": 0.62}</t>
+          <t>{"позиций": 2775, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 56, "дубли": 0.05, "мед. доля": 0.62}</t>
         </is>
       </c>
       <c r="F637" t="n">
@@ -24177,11 +24177,11 @@
         </is>
       </c>
       <c r="D655" t="n">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>{"позиций": 1129, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 34, "дубли": 0.07, "мед. доля": 0.49}</t>
+          <t>{"позиций": 1126, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 34.0, "дубли": 0.07, "мед. доля": 0.49}</t>
         </is>
       </c>
       <c r="F655" t="n">
@@ -24859,11 +24859,11 @@
         </is>
       </c>
       <c r="D674" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>{"позиций": 332, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 35.0, "дубли": 0.09, "мед. доля": 0.75}</t>
+          <t>{"позиций": 331, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 35, "дубли": 0.09, "мед. доля": 0.75}</t>
         </is>
       </c>
       <c r="F674" t="n">
@@ -25356,11 +25356,11 @@
         </is>
       </c>
       <c r="D688" t="n">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>{"позиций": 675, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 54, "дубли": 0.01, "мед. доля": 0.76}</t>
+          <t>{"позиций": 671, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 54, "дубли": 0.01, "мед. доля": 0.76}</t>
         </is>
       </c>
       <c r="F688" t="n">
@@ -25467,11 +25467,11 @@
         </is>
       </c>
       <c r="D691" t="n">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>{"позиций": 463, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 40, "дубли": 0.01, "мед. доля": 0.67}</t>
+          <t>{"позиций": 459, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 40, "дубли": 0.01, "мед. доля": 0.66}</t>
         </is>
       </c>
       <c r="F691" t="n">
@@ -25616,7 +25616,7 @@
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>{"позиций": 22, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 11.0, "дубли": 0.95, "мед. доля": 1.0}</t>
+          <t>{"позиций": 0}</t>
         </is>
       </c>
       <c r="F695" t="n">
@@ -26334,11 +26334,11 @@
         </is>
       </c>
       <c r="D715" t="n">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>{"позиций": 344, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 51.0, "дубли": 0.01, "мед. доля": 0.7}</t>
+          <t>{"позиций": 330, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 52.5, "дубли": 0.02, "мед. доля": 0.69}</t>
         </is>
       </c>
       <c r="F715" t="n">
@@ -27241,11 +27241,11 @@
         </is>
       </c>
       <c r="D740" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>{"позиций": 138, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 85.0, "дубли": 0.0, "мед. доля": 0.83}</t>
+          <t>{"позиций": 137, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 85, "дубли": 0.0, "мед. доля": 0.83}</t>
         </is>
       </c>
       <c r="F740" t="n">
@@ -27605,11 +27605,11 @@
         </is>
       </c>
       <c r="D750" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>{"позиций": 83, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 54, "дубли": 0.0, "мед. доля": 0.8}</t>
+          <t>{"позиций": 82, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 54.0, "дубли": 0.0, "мед. доля": 0.79}</t>
         </is>
       </c>
       <c r="F750" t="n">
@@ -27901,11 +27901,11 @@
         </is>
       </c>
       <c r="D758" t="n">
-        <v>1490</v>
+        <v>1458</v>
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>{"позиций": 1490, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 47.0, "дубли": 0.03, "мед. доля": 0.65}</t>
+          <t>{"позиций": 1458, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 48.0, "дубли": 0.02, "мед. доля": 0.66}</t>
         </is>
       </c>
       <c r="F758" t="n">
@@ -28660,11 +28660,11 @@
         </is>
       </c>
       <c r="D779" t="n">
-        <v>240</v>
+        <v>125</v>
       </c>
       <c r="E779" t="inlineStr">
         <is>
-          <t>{"позиций": 240, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 71.0, "дубли": 0.1, "мед. доля": 0.8}</t>
+          <t>{"позиций": 125, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 55, "дубли": 0.0, "мед. доля": 0.62}</t>
         </is>
       </c>
       <c r="F779" t="n">
@@ -30311,11 +30311,11 @@
         </is>
       </c>
       <c r="D825" t="n">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="E825" t="inlineStr">
         <is>
-          <t>{"позиций": 617, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 45, "дубли": 0.02, "мед. доля": 0.52}</t>
+          <t>{"позиций": 608, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 45.0, "дубли": 0.0, "мед. доля": 0.51}</t>
         </is>
       </c>
       <c r="F825" t="n">
@@ -31616,11 +31616,11 @@
         </is>
       </c>
       <c r="D861" t="n">
-        <v>807</v>
+        <v>792</v>
       </c>
       <c r="E861" t="inlineStr">
         <is>
-          <t>{"позиций": 807, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 55, "дубли": 0.0, "мед. доля": 0.75}</t>
+          <t>{"позиций": 792, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 55.0, "дубли": 0.0, "мед. доля": 0.75}</t>
         </is>
       </c>
       <c r="F861" t="n">
@@ -33282,11 +33282,11 @@
         </is>
       </c>
       <c r="D907" t="n">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E907" t="inlineStr">
         <is>
-          <t>{"позиций": 366, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 24.0, "дубли": 0.04, "мед. доля": 0.61}</t>
+          <t>{"позиций": 364, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 24.0, "дубли": 0.04, "мед. доля": 0.6}</t>
         </is>
       </c>
       <c r="F907" t="n">
@@ -35751,7 +35751,7 @@
       </c>
       <c r="E975" t="inlineStr">
         <is>
-          <t>{"позиций": 2, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 6.0, "дубли": 0.5, "мед. доля": 1.0}</t>
+          <t>{"позиций": 0}</t>
         </is>
       </c>
       <c r="F975" t="n">
@@ -36148,11 +36148,11 @@
         </is>
       </c>
       <c r="D986" t="n">
-        <v>2556</v>
+        <v>2553</v>
       </c>
       <c r="E986" t="inlineStr">
         <is>
-          <t>{"позиций": 2556, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 59.0, "дубли": 0.09, "мед. доля": 0.62}</t>
+          <t>{"позиций": 2553, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 59, "дубли": 0.09, "мед. доля": 0.62}</t>
         </is>
       </c>
       <c r="F986" t="n">
@@ -36722,11 +36722,11 @@
         </is>
       </c>
       <c r="D1002" t="n">
-        <v>1855</v>
+        <v>1851</v>
       </c>
       <c r="E1002" t="inlineStr">
         <is>
-          <t>{"позиций": 1855, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 39, "дубли": 0.03, "мед. доля": 0.58}</t>
+          <t>{"позиций": 1851, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 39, "дубли": 0.03, "мед. доля": 0.58}</t>
         </is>
       </c>
       <c r="F1002" t="n">
@@ -37706,11 +37706,11 @@
         </is>
       </c>
       <c r="D1029" t="n">
-        <v>809</v>
+        <v>750</v>
       </c>
       <c r="E1029" t="inlineStr">
         <is>
-          <t>{"позиций": 809, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 51, "дубли": 0.0, "мед. доля": 0.61}</t>
+          <t>{"позиций": 750, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 50.0, "дубли": 0.0, "мед. доля": 0.58}</t>
         </is>
       </c>
       <c r="F1029" t="n">
@@ -38070,11 +38070,11 @@
         </is>
       </c>
       <c r="D1039" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E1039" t="inlineStr">
         <is>
-          <t>{"позиций": 174, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 58.0, "дубли": 0.01, "мед. доля": 0.89}</t>
+          <t>{"позиций": 173, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 58, "дубли": 0.01, "мед. доля": 0.89}</t>
         </is>
       </c>
       <c r="F1039" t="n">
@@ -38248,15 +38248,15 @@
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>чисто</t>
+          <t>не прошло ворота</t>
         </is>
       </c>
       <c r="D1044" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="E1044" t="inlineStr">
         <is>
-          <t>{"позиций": 540, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 92.0, "дубли": 0.0, "мед. доля": 0.84}</t>
+          <t>{"позиций": 0}</t>
         </is>
       </c>
       <c r="F1044" t="n">
@@ -38326,11 +38326,11 @@
         </is>
       </c>
       <c r="D1046" t="n">
-        <v>2847</v>
+        <v>2838</v>
       </c>
       <c r="E1046" t="inlineStr">
         <is>
-          <t>{"позиций": 2847, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 52, "дубли": 0.08, "мед. доля": 0.54}</t>
+          <t>{"позиций": 2838, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 52.0, "дубли": 0.08, "мед. доля": 0.55}</t>
         </is>
       </c>
       <c r="F1046" t="n">
@@ -39647,11 +39647,11 @@
         </is>
       </c>
       <c r="D1083" t="n">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E1083" t="inlineStr">
         <is>
-          <t>{"позиций": 364, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 44.0, "дубли": 0.05, "мед. доля": 0.5}</t>
+          <t>{"позиций": 363, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 44, "дубли": 0.05, "мед. доля": 0.5}</t>
         </is>
       </c>
       <c r="F1083" t="n">
@@ -40409,11 +40409,11 @@
         </is>
       </c>
       <c r="D1104" t="n">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="E1104" t="inlineStr">
         <is>
-          <t>{"позиций": 1143, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 84, "дубли": 0.01, "мед. доля": 0.81}</t>
+          <t>{"позиций": 1142, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 83.5, "дубли": 0.01, "мед. доля": 0.81}</t>
         </is>
       </c>
       <c r="F1104" t="n">
@@ -41128,11 +41128,11 @@
         </is>
       </c>
       <c r="D1124" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E1124" t="inlineStr">
         <is>
-          <t>{"позиций": 105, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 39, "дубли": 0.05, "мед. доля": 0.72}</t>
+          <t>{"позиций": 104, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 39.0, "дубли": 0.05, "мед. доля": 0.72}</t>
         </is>
       </c>
       <c r="F1124" t="n">
@@ -42285,11 +42285,11 @@
         </is>
       </c>
       <c r="D1156" t="n">
-        <v>1491</v>
+        <v>1465</v>
       </c>
       <c r="E1156" t="inlineStr">
         <is>
-          <t>{"позиций": 1491, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 73, "дубли": 0.02, "мед. доля": 0.8}</t>
+          <t>{"позиций": 1465, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 73, "дубли": 0.01, "мед. доля": 0.8}</t>
         </is>
       </c>
       <c r="F1156" t="n">
@@ -42464,11 +42464,11 @@
         </is>
       </c>
       <c r="D1161" t="n">
-        <v>2220</v>
+        <v>2217</v>
       </c>
       <c r="E1161" t="inlineStr">
         <is>
-          <t>{"позиций": 2220, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 76.5, "дубли": 0.03, "мед. доля": 0.71}</t>
+          <t>{"позиций": 2217, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 77, "дубли": 0.03, "мед. доля": 0.71}</t>
         </is>
       </c>
       <c r="F1161" t="n">
@@ -43001,11 +43001,11 @@
         </is>
       </c>
       <c r="D1176" t="n">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="E1176" t="inlineStr">
         <is>
-          <t>{"позиций": 362, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 37.0, "дубли": 0.0, "мед. доля": 0.57}</t>
+          <t>{"позиций": 352, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 38.0, "дубли": 0.0, "мед. доля": 0.58}</t>
         </is>
       </c>
       <c r="F1176" t="n">
@@ -43464,11 +43464,11 @@
         </is>
       </c>
       <c r="D1189" t="n">
-        <v>1118</v>
+        <v>1091</v>
       </c>
       <c r="E1189" t="inlineStr">
         <is>
-          <t>{"позиций": 1118, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 71.0, "дубли": 0.06, "мед. доля": 0.7}</t>
+          <t>{"позиций": 1091, "с ценой": 1.0, "UI-мусор": 0.0, "мед. длина": 71, "дубли": 0.06, "мед. доля": 0.69}</t>
         </is>
       </c>
       <c r="F1189" t="n">
@@ -43953,800 +43953,800 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ilab-clinic.ru</t>
+          <t>krasnodar.skinerica-clinic.ru</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1500</v>
+        <v>14000</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Прием (осмотр, консультация) врача-терапевта первичный Седова Е.В</t>
+          <t>зона вокруг губ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ilab-clinic.ru</t>
+          <t>krasnodar.skinerica-clinic.ru</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3000</v>
+        <v>24000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Прием (осмотр, консультация) врача-невролога первичный</t>
+          <t>зона вокруг глаз</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ilab-clinic.ru</t>
+          <t>krasnodar.skinerica-clinic.ru</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3000</v>
+        <v>45000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Первичный прием врача-гастроэнтеролога</t>
+          <t>щеки до подбородка, уменьшение носогубных складок, область вокруг губ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ilab-clinic.ru</t>
+          <t>krasnodar.skinerica-clinic.ru</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3000</v>
+        <v>30000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Прием (неинстументальный осмотр, консультация) врача-офтальмолога первичный</t>
+          <t>второй подбородок, овал лица</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ilab-clinic.ru</t>
+          <t>krasnodar.skinerica-clinic.ru</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3000</v>
+        <v>30000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Прием (осмотр, консультация) врача-дерматовенеролога первичный</t>
+          <t>включая второй подбородок</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ilab-clinic.ru</t>
+          <t>krasnodar.skinerica-clinic.ru</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>150</v>
+        <v>98000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Пульсоксиметрия</t>
+          <t>название Лицо+шея+декольте, 1100-1400 линий +4 900 бонусов</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ilab-clinic.ru</t>
+          <t>krasnodar.skinerica-clinic.ru</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>500</v>
+        <v>80000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Офтальмоскопия прямая</t>
+          <t>название Талия (жировые отложения), 1500-2100 линий +4 000 бонусов</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:14</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ilab-clinic.ru</t>
+          <t>krasnodar.skinerica-clinic.ru</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>500</v>
+        <v>120000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Биомикроскопия глаза</t>
+          <t>название Живот+бока, 3000-4200 линий +6 000 бонусов</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:14</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>clinsev.ru</t>
+          <t>clinicred.ru</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1300</v>
+        <v>99000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Рентгенография турецкого седла в 1-ой проекции</t>
+          <t>Постакне и глубокие рубцы больше не приговор для рельефа вашей кожи. Мы объединили две самые эффективные методики в один</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>clinsev.ru</t>
+          <t>clinicred.ru</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1600</v>
+        <v>35000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Рентгенография придаточных пазух носа 2 снимка</t>
+          <t>Главное преимущество комплекса — сочетание глубокого увлажнения и фототерапии позволяет одновременно улучшить качество к</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>clinsev.ru</t>
+          <t>clinicred.ru</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1600</v>
+        <v>15000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Рентгенография придаточных пазух носа</t>
+          <t>сначала определяем причину и состояние волос, а затем воздействуем на проблему комплексно, стимулируя кожу головы и подд</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>clinsev.ru</t>
+          <t>clinicred.ru</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1650</v>
+        <v>35000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Рентгенография костей носа</t>
+          <t>Комплексная коррекция мимики сразу в нескольких зонах, чтобы лицо выглядело гладким, свежим и естественно отдохнувшим</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>clinsev.ru</t>
+          <t>clinicred.ru</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2100</v>
+        <v>4500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Рентгенография височной кости (2 снимка)</t>
+          <t>Во время консультации врач проводит диагностику кожи с помощью аппарата Janus Pro Sunlite, что позволяет более точно опр</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>clinsev.ru</t>
+          <t>clinicred.ru</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1850</v>
+        <v>6000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Рентгенография шейных позвонков 1 и 2-го в прямой проекции через открытый рот</t>
+          <t>Мы применяем современные методы и технологии, которые позволяют достичь видимых и долгосрочных результатов в уходе за ко</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>clinsev.ru</t>
+          <t>clinicred.ru</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3000</v>
+        <v>5200</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Рентгенография шейного отдела с функциональными пробами в четырех проекциях</t>
+          <t>Мы предлагаем услуги эстетической косметологии с применением премиальных средств профессионального ухода</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>clinsev.ru</t>
+          <t>clinicred.ru</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1650</v>
+        <v>5800</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Рентгенография шейного отдела позвоночника в двух проекциях</t>
+          <t>Специалист в зависимости от потребностей пациента и его особенностей может предложить различные варианты инъекционной ко</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>medprofika.ru</t>
+          <t>medici124.ru</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>360</v>
+        <v>2000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Геморрагический синдром (кровоточивость, свертываемость)</t>
+          <t>Микротоки</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>паттерн:241</t>
+          <t>паттерн:47</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>medprofika.ru</t>
+          <t>medici124.ru</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>420</v>
+        <v>2500</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Группа крови и резус-фактор</t>
+          <t>Хиромассаж</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>паттерн:241</t>
+          <t>паттерн:47</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>medprofika.ru</t>
+          <t>medici124.ru</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>410</v>
+        <v>3000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Общий анализ крови (без СОЭ, с «ручным» подсчетом лейкоцитарной формулы)</t>
+          <t>Хиромассаж (1)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>паттерн:241</t>
+          <t>паттерн:47</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>medprofika.ru</t>
+          <t>medici124.ru</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>500</v>
+        <v>5500</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Общий анализ крови (СОЭ, с «ручным» подсчетом лейкоцитарной формулы)</t>
+          <t>Чистка Cellcosmet</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>паттерн:241</t>
+          <t>паттерн:47</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>medprofika.ru</t>
+          <t>medici124.ru</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>450</v>
+        <v>4500</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Подсчет тромбоцитов по Фонио</t>
+          <t>Чистка Holy Land</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>паттерн:241</t>
+          <t>паттерн:47</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>medprofika.ru</t>
+          <t>medici124.ru</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>250</v>
+        <v>2500</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ретикулоциты</t>
+          <t>Чистка механическая 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>паттерн:241</t>
+          <t>паттерн:47</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>medprofika.ru</t>
+          <t>medici124.ru</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>700</v>
+        <v>4500</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>G15 Аллерген пшеницы культивированной, IgE</t>
+          <t>Чистка с ультразвуком (комбинированная)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>паттерн:241</t>
+          <t>паттерн:47</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>medprofika.ru</t>
+          <t>medici124.ru</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2300</v>
+        <v>1000</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Аллерген артикаин/ультракаин, IgE</t>
+          <t>Баночный массаж</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>паттерн:241</t>
+          <t>паттерн:47</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>spabarhat.ru</t>
+          <t>ugmedtrans.ru</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3990</v>
+        <v>2500</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>EVE Lab — ИИ-диагностика кожи</t>
+          <t>Индивидуальное занятие ЛФК с отоневрологом</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>паттерн:20</t>
+          <t>таблица</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>spabarhat.ru</t>
+          <t>ugmedtrans.ru</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11900</v>
+        <v>3500</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ультразвуковой SMAS-лифтинг на аппарате UCOS-HIFU</t>
+          <t>Прием (осмотр, консультация) врача-отоневролога первичный</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>паттерн:20</t>
+          <t>таблица</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>spabarhat.ru</t>
+          <t>ugmedtrans.ru</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>20000</v>
+        <v>2800</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Микроигольчатый RF-лифтинг SYLFIRM X</t>
+          <t>Прием (осмотр, консультация) врача-отоневролога повторный</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>паттерн:20</t>
+          <t>таблица</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>spabarhat.ru</t>
+          <t>ugmedtrans.ru</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4590</v>
+        <v>1500</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Укрепление и омоложение лица на аппарате Icoone Laser Med</t>
+          <t>Прием (осмотр, консультация) врача по медицинской профилактике первичный</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>паттерн:20</t>
+          <t>таблица</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>spabarhat.ru</t>
+          <t>ugmedtrans.ru</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>9900</v>
+        <v>2800</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Генетические тесты</t>
+          <t>Прием (осмотр, консультация) врача гастроэнтеролога первичный</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>паттерн:20</t>
+          <t>таблица</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>spabarhat.ru</t>
+          <t>ugmedtrans.ru</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>17990</v>
+        <v>2300</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Экзосомальная терапия с использованием NANOPORE</t>
+          <t>Прием (осмотр, консультация) врача гастроэнтеролога повторный</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>паттерн:20</t>
+          <t>таблица</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>spabarhat.ru</t>
+          <t>ugmedtrans.ru</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2000</v>
+        <v>3300</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Консультация врача – дерматокосметолога</t>
+          <t>Прием (осмотр, консультация) врача-онколога (маммолога) первичный</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>паттерн:20</t>
+          <t>таблица</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>spabarhat.ru</t>
+          <t>ugmedtrans.ru</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5000</v>
+        <v>2900</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Экспресс-уход "OXY REFRESH"</t>
+          <t>Прием (осмотр, консультация) врача-онколога (маммолога) повторный</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>паттерн:20</t>
+          <t>таблица</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>art-medica.ru</t>
+          <t>avantis-stom.ru</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3000</v>
+        <v>14900</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Первичная консультация дерматолога Прием пациента, сбор анамнеза заболевания, объективный осмотр, определение необходимо</t>
+          <t>Металлическая лигатурная брекет-система BioMIM(США)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:12</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>art-medica.ru</t>
+          <t>avantis-stom.ru</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Повторная консультация дерматолога Прием пациента, разъяснение пациенту информации о результатах обследования, объективн</t>
+          <t>Первичная консультация ортодонта</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:12</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>art-medica.ru</t>
+          <t>avantis-stom.ru</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Первичная консультация трихолога с диагностикой волос Прием пациента, сбор анамнеза заболевания, объективный осмотр, опр</t>
+          <t>Диагностика стандарт</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:12</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>art-medica.ru</t>
+          <t>avantis-stom.ru</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Повторная консультация трихолога Прием пациента, разъяснение пациенту информации о результатах обследования, объективный</t>
+          <t>Диагностика цифровая</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:12</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>art-medica.ru</t>
+          <t>avantis-stom.ru</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3000</v>
+        <v>39000</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Гистологическое исследование биоптата кожи</t>
+          <t>Металлические самолигирующие брекеты H4(США)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:12</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>art-medica.ru</t>
+          <t>avantis-stom.ru</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1000</v>
+        <v>39000</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Дерматоскопия</t>
+          <t>Металлические самолигирующие брекеты DamonQ2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:12</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>art-medica.ru</t>
+          <t>avantis-stom.ru</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>5000</v>
+        <v>58000</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Панч-биопсия кожи</t>
+          <t>Керамические самолигирующие брекеты DamonClear</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:12</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>art-medica.ru</t>
+          <t>avantis-stom.ru</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>800</v>
+        <v>32000</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Криодеструкция бородавок, папиллом</t>
+          <t>Аппарат Дерихсвайлера</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:12</t>
         </is>
       </c>
     </row>
@@ -44913,135 +44913,135 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>profosmotr.gippokrates.ru</t>
+          <t>rostov.upclinic.ru</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1350</v>
+        <v>94900</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Первичный прием врача-терапевта</t>
+          <t>пациентов</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>profosmotr.gippokrates.ru</t>
+          <t>rostov.upclinic.ru</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>800</v>
+        <v>93400</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Повторный прием врача-терапевта</t>
+          <t>ПРОКТОЛОГИЯ</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>profosmotr.gippokrates.ru</t>
+          <t>rostov.upclinic.ru</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1400</v>
+        <v>67800</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Первичный прием врача-терапевта,педиатра</t>
+          <t>ДЕРМАТОЛОГИЯ</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>profosmotr.gippokrates.ru</t>
+          <t>rostov.upclinic.ru</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2000</v>
+        <v>59600</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Первичный прием клинического психолога</t>
+          <t>ГИНЕКОЛОГИЯ</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>profosmotr.gippokrates.ru</t>
+          <t>rostov.upclinic.ru</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1500</v>
+        <v>26100</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Первичный прием врача-психотерапевта</t>
+          <t>КОСМЕТОЛОГИЯ</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>profosmotr.gippokrates.ru</t>
+          <t>rostov.upclinic.ru</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2500</v>
+        <v>13400</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Гипнотерапия</t>
+          <t>ТРИХОЛОГИЯ</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>profosmotr.gippokrates.ru</t>
+          <t>rostov.upclinic.ru</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2000</v>
+        <v>85000</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Индивидуальное психо-коррекционное занятие</t>
+          <t>Базовая операция с использованием местной анестезии</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -45053,15 +45053,15 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>profosmotr.gippokrates.ru</t>
+          <t>rostov.upclinic.ru</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1100</v>
+        <v>120000</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Первичный прием врача-акушера-гинеколога</t>
+          <t>Операция с установкой специального импланта для лучшей фиксации</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -45073,975 +45073,975 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>dentalroom-msk.ru</t>
+          <t>clinicvk.ru</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2500</v>
+        <v>1400</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Обучение гигиене полости рта и зубов индивидуальное, подбор средств и предметов гигиены полости рта</t>
+          <t>Прием (осмотр, консультация) врача-косметолога первичный</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:309</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>dentalroom-msk.ru</t>
+          <t>clinicvk.ru</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>5000</v>
+        <v>1700</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Профессиональная гигиена полости рта (снятие мягких и твердых наддесневых отложений с ремотерапией (временный прикус))</t>
+          <t>Прием (осмотр, консультация) врача-дерматовенеролога первичный</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:309</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>dentalroom-msk.ru</t>
+          <t>clinicvk.ru</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>7000</v>
+        <v>1100</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Профессиональная гигиена полости рта (снятие мягких и твердых наддесневых отложений с ремотерапией (сменный прикус))</t>
+          <t>Прием (осмотр, консультация) врача-дерматовенеролога повторный</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:309</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>dentalroom-msk.ru</t>
+          <t>clinicvk.ru</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>9000</v>
+        <v>2200</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Профессиональная гигиена полости рта (снятие мягких и твердых наддесневых отложений до 18 лет с ремотерапией)</t>
+          <t>Прием (осмотр, консультация) врача-трихолога первичный</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:309</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>dentalroom-msk.ru</t>
+          <t>clinicvk.ru</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>11500</v>
+        <v>1600</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Профессиональная гигиена полости рта (снятие мягких и твердых наддесневых отложений после 18 лет с ремотерапией)</t>
+          <t>Прием (осмотр, консультация) врача-трихолога повторный</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:309</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>dentalroom-msk.ru</t>
+          <t>clinicvk.ru</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>13500</v>
+        <v>3500</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Профессиональная гигиена полости рта при заболеваниях пародонта (чистка карманов до 4мм)</t>
+          <t>Прием (осмотр, консультация) врача-пластического хирурга первичный</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:309</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>dentalroom-msk.ru</t>
+          <t>clinicvk.ru</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>15000</v>
+        <v>29200</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Профессиональная гигиена полости рта (с брекет-системой, после снятия брекет-системы)</t>
+          <t>Введение искусственных наполнителей в мягкие ткани с целью коррекции формы: Radiesse 1,5 мл (Германия)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:309</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>dentalroom-msk.ru</t>
+          <t>clinicvk.ru</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>15000</v>
+        <v>42500</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Профессиональная гигиена полости рта (снятие аттачментов после ортодонтичнеского лечения)</t>
+          <t>Введение искусственных наполнителей в мягкие ткани с целью коррекции формы: Radiesse 3 мл (Германия)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:309</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>mcvrach.ru</t>
+          <t>euromednsk.ru</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>3000</v>
+        <v>14000</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Тургеневская</t>
+          <t>Ингаляционная анестезия (севофлюран) + ИВЛ дополнительно 1 час (свыше 2х часов)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>паттерн:20</t>
+          <t>pdf</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>mcvrach.ru</t>
+          <t>euromednsk.ru</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Коммунистический</t>
+          <t>Ингаляционная анестезия (севофлюран) в педиатрии, до 30мин, с последующим наблюдением до 2-х часов</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>паттерн:20</t>
+          <t>pdf</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>mcvrach.ru</t>
+          <t>euromednsk.ru</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4500</v>
+        <v>10000</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Тургеневская</t>
+          <t>Комбинированная анестезия (спинально-эпидуральная и др.), дополнительный час</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>паттерн:20</t>
+          <t>pdf</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>mcvrach.ru</t>
+          <t>euromednsk.ru</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3500</v>
+        <v>21000</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Коммунистический</t>
+          <t>Комплекс интенсивной терапии, вариант 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>паттерн:20</t>
+          <t>pdf</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>mcvrach.ru</t>
+          <t>euromednsk.ru</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1500</v>
+        <v>8000</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Тургеневская</t>
+          <t>Местная анестезия в пластической хирургии, 1-ый час</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>паттерн:20</t>
+          <t>pdf</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>mcvrach.ru</t>
+          <t>euromednsk.ru</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1300</v>
+        <v>5000</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Коммунистический</t>
+          <t>Местная анестезия в стационаре</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>паттерн:20</t>
+          <t>pdf</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>mcvrach.ru</t>
+          <t>euromednsk.ru</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1300</v>
+        <v>7000</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Тургеневская</t>
+          <t>Местная анестезия+внутривенная седация, дополнительный час (свыше 2х часов)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>паттерн:20</t>
+          <t>pdf</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>mcvrach.ru</t>
+          <t>euromednsk.ru</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1750</v>
+        <v>19000</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Тургеневская</t>
+          <t>Проводниковая анестезия + седация, до 2х часов</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>паттерн:20</t>
+          <t>pdf</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>sportmed54.ru</t>
+          <t>tolyatti.rezonans-clinic.ru</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1600</v>
+        <v>2200</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Программа медицинского осмотра укороченная для забегов и полумарафонов (форма 073у)</t>
+          <t>Первичный прием акушера-гинеколога</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>паттерн:5</t>
+          <t>pdf</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>sportmed54.ru</t>
+          <t>tolyatti.rezonans-clinic.ru</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>3900</v>
+        <v>2200</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Программа медицинского осмотра для забегов и полумарафонов от 15 км. (взрослые)</t>
+          <t>Первичный прием врача-гастроэнтеролога</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>паттерн:5</t>
+          <t>pdf</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>sportmed54.ru</t>
+          <t>tolyatti.rezonans-clinic.ru</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3600</v>
+        <v>2200</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Этап спортивного оздоровления и начальной подготовки (дети и подростки)</t>
+          <t>Первичный прием врача-кардиолога</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>паттерн:5</t>
+          <t>pdf</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>sportmed54.ru</t>
+          <t>tolyatti.rezonans-clinic.ru</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>3900</v>
+        <v>4000</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Программа мединского осмотра на тренировочном этапе</t>
+          <t>Прием врача мануальной терапии с применением мягких манипуляционных методик (вес до 120 кг)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>паттерн:5</t>
+          <t>pdf</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>sportmed54.ru</t>
+          <t>tolyatti.rezonans-clinic.ru</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>3900</v>
+        <v>2200</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Медосмотр на этапе совершенствования спортивного мастерства</t>
+          <t>Первичный прием врача-невролога</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>паттерн:5</t>
+          <t>pdf</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>sportmed54.ru</t>
+          <t>tolyatti.rezonans-clinic.ru</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1200</v>
+        <v>2200</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>УЗИ мягких тканей</t>
+          <t>Первичный прием врача-ревматолога</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>паттерн:6</t>
+          <t>pdf</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>sportmed54.ru</t>
+          <t>tolyatti.rezonans-clinic.ru</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2700</v>
+        <v>2200</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>УЗИ органов брюшной полости</t>
+          <t>Первичный прием травматолога-ортопеда</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>паттерн:6</t>
+          <t>pdf</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>sportmed54.ru</t>
+          <t>tolyatti.rezonans-clinic.ru</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>УЗИ гинекологическое (трансабдоминально) с доплерографией</t>
+          <t>Первичный прием врача-терапевта</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>паттерн:6</t>
+          <t>pdf</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>bc.clinic</t>
+          <t>b-med59.ru</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>9900</v>
+        <v>18000</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Активный лосьон для стимуляции роста волос Повышает прочность и активирует рост волос. Укрепляет и защищает фолликулы и </t>
+          <t>Процедура EMFACE: Лоб</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>паттерн:18</t>
+          <t>паттерн:7</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>bc.clinic</t>
+          <t>b-med59.ru</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3200</v>
+        <v>18000</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Шампунь активатор Эффективное очищение для кожи головы с выраженным тонизирующим и разогревающим эффектом. Усиливает кро</t>
+          <t>Процедура EMFACE: Зона под глазами</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>паттерн:18</t>
+          <t>паттерн:7</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>bc.clinic</t>
+          <t>b-med59.ru</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>11900</v>
+        <v>18000</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Био-энерджи экзосомально-пептидный стимулятор роста волос Увеличивает толщину стержней, восстанавливает плотность и густ</t>
+          <t>Процедура EMFACE: Щеки</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>паттерн:18</t>
+          <t>паттерн:7</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>bc.clinic</t>
+          <t>b-med59.ru</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>5490</v>
+        <v>18000</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Очищающая пенка для лица Photoceutical Foaming Cleanser Пенка предназначена для очищения и ухода за лицом от UF излучени</t>
+          <t>Процедура EMFACE: Субментальная зона</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>паттерн:18</t>
+          <t>паттерн:7</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>bc.clinic</t>
+          <t>b-med59.ru</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>5690</v>
+        <v>32000</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Крем солнцезащитный для лица и тела TiZO Ultra zinc Tinted, SPF40 Солнцезащитный увлажняющий крем c тоном, 100мл. США</t>
+          <t>Процедура EMFACE: 2 зоны</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>паттерн:18</t>
+          <t>паттерн:7</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>bc.clinic</t>
+          <t>b-med59.ru</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>5690</v>
+        <v>45000</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Крем солнцезащитный для лица и тела TiZO Ultra zinc NON-tinted, SPF40 Солнцезащитный увлажняющий крем без тона, 100мл. С</t>
+          <t>Процедура EMFACE: 3 зоны</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>паттерн:18</t>
+          <t>паттерн:7</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>bc.clinic</t>
+          <t>b-med59.ru</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>6990</v>
+        <v>58000</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Solar Defense Tinted SPF 30 крем для лица с тональным эффектом Солнцезащитный увлажняющий крем для лица с тональным эффе</t>
+          <t>Процедура EMFACE 4 зоны</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>паттерн:18</t>
+          <t>паттерн:7</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>bc.clinic</t>
+          <t>b-med59.ru</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>12900</v>
+        <v>20000</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Retinol Routine BOOSTER Ретиноловый бустер 1% Ретиноловый бустер 1% с обновляющим и уплотняющим действием, 30мл</t>
+          <t>FOTONA 4D: Лицо (без глаз)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>паттерн:18</t>
+          <t>паттерн:852</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>regionmed72.ru</t>
+          <t>natalivrn.ru</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1976</v>
+        <v>8000</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Санаторно - курортная карта</t>
+          <t>Прикорневой объем Boost up (Буст ап)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>паттерн:140</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>regionmed72.ru</t>
+          <t>natalivrn.ru</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>5186</v>
+        <v>3500</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Справка для учебы</t>
+          <t>Прическа</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>паттерн:140</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>regionmed72.ru</t>
+          <t>natalivrn.ru</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1050</v>
+        <v>1300</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Справка в бассейн</t>
+          <t>Стрижка детская до 7 лет</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>паттерн:140</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>regionmed72.ru</t>
+          <t>natalivrn.ru</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1940</v>
+        <v>3000</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Справка-допуск (ГТО), для занятий спортом</t>
+          <t>Стрижка женская / мужская</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>паттерн:140</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>regionmed72.ru</t>
+          <t>natalivrn.ru</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>4830</v>
+        <v>4700</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Справка для госслужбы</t>
+          <t>Окрашивание</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>паттерн:140</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>regionmed72.ru</t>
+          <t>natalivrn.ru</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>4590</v>
+        <v>6100</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Справка для следственных органов</t>
+          <t>Окрашивание + стрижка</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>паттерн:140</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>regionmed72.ru</t>
+          <t>natalivrn.ru</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>4902</v>
+        <v>16500</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Справка для судей</t>
+          <t>Комплект</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>паттерн:140</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>regionmed72.ru</t>
+          <t>natalivrn.ru</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>2350</v>
+        <v>11000</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Справка на гостайну</t>
+          <t>Наращивание волос: полукомплект</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>паттерн:140</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>facebody.ru</t>
+          <t>doctordr.ru</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Верхняя губа</t>
+          <t>Первичная консультация гинеколога-эксперта ( )</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:964</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>facebody.ru</t>
+          <t>doctordr.ru</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1650</v>
+        <v>3000</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Межбровная область</t>
+          <t>Повторная консультация гинеколога-эксперта в теч. месяца</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:964</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>facebody.ru</t>
+          <t>doctordr.ru</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1000</v>
+        <v>18000</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Носовые ходы</t>
+          <t>Гистероскопия с маточным кюретажем под общим наркозом. Требуется предварительная сдача “госпитального комплекса”. Наркоз</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:964</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>facebody.ru</t>
+          <t>doctordr.ru</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>2600</v>
+        <v>22500</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ушные раковины</t>
+          <t xml:space="preserve">Гистерорезектоскопия 1 степени сложности под общим наркозом. Требуется предварительная сдача “госпитального комплекса”. </t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:964</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>facebody.ru</t>
+          <t>doctordr.ru</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>3700</v>
+        <v>30000</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Подбородок</t>
+          <t xml:space="preserve">Гистерорезектоскопия 2 степени сложности под общим наркозом. Требуется предварительная сдача “госпитального комплекса”. </t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:964</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>facebody.ru</t>
+          <t>doctordr.ru</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>6400</v>
+        <v>43000</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Область шеи</t>
+          <t xml:space="preserve">Гистерорезектоскопия 3 степени сложности под общим наркозом. Требуется предварительная сдача “госпитального комплекса”. </t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:964</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>facebody.ru</t>
+          <t>doctordr.ru</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>6400</v>
+        <v>7000</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Щеки + подбородок</t>
+          <t>Гистологический анализ</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:964</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>facebody.ru</t>
+          <t>doctordr.ru</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>8300</v>
+        <v>1400</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Всё лицо</t>
+          <t>Маммография, две проекции каждой молочной железы</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:964</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>artmed55.ru</t>
+          <t>arnika74.ru</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>400</v>
+        <v>120</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Забор крови</t>
+          <t>Общий холестерин, скрининг</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -46053,15 +46053,15 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>artmed55.ru</t>
+          <t>arnika74.ru</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>400</v>
+        <v>120</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Забор биоматериала</t>
+          <t>Глюкоза, скрининг</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -46073,15 +46073,15 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>artmed55.ru</t>
+          <t>arnika74.ru</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>300</v>
+        <v>160</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Забор мазка</t>
+          <t>Общий анализ мочи (физико-химические свойства), скрининг</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -46093,15 +46093,15 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>artmed55.ru</t>
+          <t>arnika74.ru</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1700</v>
+        <v>210</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>УЗИ гинекологическое трансвагинальное</t>
+          <t>Общий анализ крови (без дифференцировки лейкоцитов) + СОЭ, скрининг</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -46113,15 +46113,15 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>artmed55.ru</t>
+          <t>arnika74.ru</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1700</v>
+        <v>130</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>УЗИ гинекологическое трансабдоминальное</t>
+          <t>Офтальмологическое комплексное обследование:визометрия, биомикроскопия глаза</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -46133,15 +46133,15 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>artmed55.ru</t>
+          <t>arnika74.ru</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1800</v>
+        <v>110</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>УЗИ по установлению беременности</t>
+          <t>Оториноларинголог</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -46153,15 +46153,15 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>artmed55.ru</t>
+          <t>arnika74.ru</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1800</v>
+        <v>150</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>УЗИ беременность I триместр, до 11 недель (двухмерное )</t>
+          <t>Терапевт-Профпатолог</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -46173,15 +46173,15 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>artmed55.ru</t>
+          <t>arnika74.ru</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>900</v>
+        <v>150</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Фолликулометрия</t>
+          <t>Невролог</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -46193,415 +46193,415 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>atlantis-clinic.ru</t>
+          <t>artmed-kzn.ru</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>6000</v>
+        <v>200</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Первичная консультация врача терапевта-эндокринолога, ПревентЭйдж (PreventAge) диетолога</t>
+          <t>Инъекция (внутримышечная/ подкожная/ внутрикожная)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>pdf</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>atlantis-clinic.ru</t>
+          <t>artmed-kzn.ru</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>3500</v>
+        <v>250</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Повторная консультация врача терапевта-эндокринолога, ПревентЭйдж (PreventAge) диетолога</t>
+          <t>Инъекция внутривенная</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>pdf</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>atlantis-clinic.ru</t>
+          <t>artmed-kzn.ru</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>50000</v>
+        <v>500</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Персональное ведение пациента 1 месяц: составление меню с учетом данных анамнеза и вкусовых предпочтений, 1 раз в неделю</t>
+          <t>Внутривенная инфузия в систему (включая стоимость физраствора)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>pdf</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>atlantis-clinic.ru</t>
+          <t>artmed-kzn.ru</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>18000</v>
+        <v>500</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Новакутан ФБио Медиум / Волюм, 1 мл (Novacutan FBio Medium / Volume, 1 мл)</t>
+          <t>Ингаляторное введение лекарственных препаратов через небулайзер</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>pdf</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>atlantis-clinic.ru</t>
+          <t>artmed-kzn.ru</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>25000</v>
+        <v>1000</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Арт филлер волюм, 1,2 мл (Art Filler Volume, 1,2 мл)</t>
+          <t>Ингаляторное введение лекарственных препаратов через небулайзер препаратом беродуал, пульмикорт</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>pdf</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>atlantis-clinic.ru</t>
+          <t>artmed-kzn.ru</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>19000</v>
+        <v>2500</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Арт филлер файн лайнс, 1 мл (Art Filler Fine Lines, 1 мл)</t>
+          <t>Постановка кожной пробы с аллергеном</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>pdf</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>atlantis-clinic.ru</t>
+          <t>artmed-kzn.ru</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>33500</v>
+        <v>4000</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Радиесс, 1,5 мл (Radiesse, 1,5 мл)</t>
+          <t>Неспецифическая гипосенсибилизация (иммуноглобулин чел п/аллергический)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>pdf</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>atlantis-clinic.ru</t>
+          <t>artmed-kzn.ru</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>55000</v>
+        <v>1500</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Радиесс, 3 мл (Radiesse, 3 мл)</t>
+          <t>Извлечение ВМС (внутриматочная спираль)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>pdf</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>optimedkrs.ru</t>
+          <t>med24krd.ru</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1500</v>
+        <v>3960</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Консультативный прием врача-дерматовенеролога (первичный)</t>
+          <t>МРТ головы по акции!</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>паттерн:510</t>
+          <t>паттерн:4</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>optimedkrs.ru</t>
+          <t>med24krd.ru</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>700</v>
+        <v>12000</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Консультативный прием врача-дерматовенеролога (повторный)</t>
+          <t>МРТ молочных желез для оценки состояния имплантов</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>паттерн:510</t>
+          <t>паттерн:15</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>optimedkrs.ru</t>
+          <t>med24krd.ru</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>300</v>
+        <v>5100</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Взятие мазка</t>
+          <t>МРТ головного мозга</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>паттерн:510</t>
+          <t>паттерн:15</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>optimedkrs.ru</t>
+          <t>med24krd.ru</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>2500</v>
+        <v>5100</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Консультативный прием врача акушера-гинеколога (первичный) В стоимость приема входят 2 исследования: -Бактериологическое</t>
+          <t>МРТ гипофиза</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>паттерн:510</t>
+          <t>паттерн:15</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>optimedkrs.ru</t>
+          <t>med24krd.ru</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1700</v>
+        <v>7500</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Консультативный прием врача акушера-гинеколога (первичный) В стоимость приема входят 2 исследования: -Бактериологическое</t>
+          <t>МРТ малого таза</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>паттерн:510</t>
+          <t>паттерн:15</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>optimedkrs.ru</t>
+          <t>med24krd.ru</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1200</v>
+        <v>11500</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Консультативный приём врача акушера-гинеколога без мазков</t>
+          <t>МРТ брюшной полости и забрюшинного пространства</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>паттерн:510</t>
+          <t>паттерн:15</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>optimedkrs.ru</t>
+          <t>med24krd.ru</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>700</v>
+        <v>9400</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Консультативный прием врача акушера-гинеколога (повторный)</t>
+          <t>МРТ молочных желез для оценки состояния имплантов</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>паттерн:510</t>
+          <t>паттерн:20</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>optimedkrs.ru</t>
+          <t>med24krd.ru</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>500</v>
+        <v>15000</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Консультация гинеколога по дополнительному обследованию и лечению после проф.осмотра</t>
+          <t>МРТ молочных желез для оценки состояния имплантов с контрастированием</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>паттерн:510</t>
+          <t>паттерн:20</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>moya-clinika.com</t>
+          <t>medica-m.ru</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>3500</v>
+        <v>30015</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Приём(осмотр, консультация) врача-терапевта, первичный</t>
+          <t>online заявок на запись</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:8</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>moya-clinika.com</t>
+          <t>medica-m.ru</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>3000</v>
+        <v>1450</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Приём(осмотр, консультация) врача-терапевта, повторный(в течение 10 дней)</t>
+          <t>беременных встали на учет</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:8</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>moya-clinika.com</t>
+          <t>medica-m.ru</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1700</v>
+        <v>1366</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Приём(осмотр, консультация) врача-терапевта первичный: осмотр перед вакцинацией</t>
+          <t>пар подготовлено к беременности</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:8</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>moya-clinika.com</t>
+          <t>medica-m.ru</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Приём(осмотр, консультация) врача общей практики(семейного врача), первичный</t>
+          <t>отзывов от наших пациентов</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:8</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>moya-clinika.com</t>
+          <t>medica-m.ru</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Приём(осмотр, консультация) врача общей практики(семейного врача), повторный(в течение 10 дней)</t>
+          <t>Первичная консультация врача-терапевта</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -46613,15 +46613,15 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>moya-clinika.com</t>
+          <t>medica-m.ru</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Прием (осмотр, консультация) врача общей практики (семейного врача) первичный: осмотр детей до 1 года (до 60 минут, перв</t>
+          <t>Первичная консультация врача-гастроэнтеролога</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -46633,15 +46633,15 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>moya-clinika.com</t>
+          <t>medica-m.ru</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>3500</v>
+        <v>2900</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Приём(осмотр, консультация) врача общей практики(семейного врача), первичный: осмотр детей до 1 года(до 40 минут, визит </t>
+          <t>Первичная консультация врача-маммолога</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -46653,15 +46653,15 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>moya-clinika.com</t>
+          <t>medica-m.ru</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>3200</v>
+        <v>4800</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Прием(осмотр, консультация) врача общей практики: осмотр детей до 1 года, повторный (до 40 минут, в течение 10 дней)</t>
+          <t>Первичная консультация врача иммунолога-аллерголога, к.м.н</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -46813,767 +46813,767 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>imedsvetliy.ru</t>
+          <t>gimenei74.ru</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>4500</v>
+        <v>3000</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>25 мин. врач высшей категории, стаж 18 + лет, Фарина Ю.А</t>
+          <t>Прием (осмотр, консультация) главного врача акушера-гинеколога</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>паттерн:18</t>
+          <t>паттерн:8</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>imedsvetliy.ru</t>
+          <t>gimenei74.ru</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>25 мин. врач высшей категории, стаж 18 + лет, Фарина Ю.А</t>
+          <t>Прием (осмотр, консультация) врача акушера-гинеколога, первичный</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>паттерн:18</t>
+          <t>паттерн:8</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>imedsvetliy.ru</t>
+          <t>gimenei74.ru</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>25 мин. стаж 6 + лет, ординатор Фариной Ю.А</t>
+          <t>Прием (осмотр, консультация) врача акушера-гинеколога, повторный</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>паттерн:18</t>
+          <t>паттерн:8</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>imedsvetliy.ru</t>
+          <t>gimenei74.ru</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>25 мин. стаж 6 + лет, ординатор Фариной Ю.А</t>
+          <t>Прием (осмотр, консультация) врача акушера-гинеколога, кандидата медицинских наук, первичный</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>паттерн:18</t>
+          <t>паттерн:8</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>imedsvetliy.ru</t>
+          <t>gimenei74.ru</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>6000</v>
+        <v>2500</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Вызов врача специалиста</t>
+          <t>Прием (осмотр, консультация) врача акушера-гинеколога, кандидата медицинских наук, повторный</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>паттерн:18</t>
+          <t>паттерн:8</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>imedsvetliy.ru</t>
+          <t>gimenei74.ru</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>1785</v>
+        <v>3500</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>По назначению лечащего врача. По предварительной записи</t>
+          <t>Прием акушера-гинеколога беременной с осмотром и постановкой на учет</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>паттерн:18</t>
+          <t>паттерн:8</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>imedsvetliy.ru</t>
+          <t>gimenei74.ru</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>2975</v>
+        <v>4500</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>По назначению лечащего врача. По предварительной записи</t>
+          <t>Прием (осмотр, консультация) врача акушера-гинеколога, доктора медицинских наук первичный</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>паттерн:18</t>
+          <t>паттерн:8</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>imedsvetliy.ru</t>
+          <t>gimenei74.ru</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>4165</v>
+        <v>3500</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>По назначению лечащего врача. По предварительной записи</t>
+          <t>Прием (осмотр, консультация) врача акушера-гинеколога, доктора медицинских наук повторный</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>паттерн:18</t>
+          <t>паттерн:8</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>cosmetologist.ru</t>
+          <t>c9m.ru</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>850</v>
+        <v>13500</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Кинезиотейпирование простое,1 зона</t>
+          <t>контракта</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:21</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>cosmetologist.ru</t>
+          <t>c9m.ru</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>1700</v>
+        <v>23080</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Кинезиотейпирование сложное, 1 зона</t>
+          <t>Программа «Осмотр малыша в 1 год»</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:14</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>cosmetologist.ru</t>
+          <t>c9m.ru</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>1200</v>
+        <v>24270</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Кинезиотейпирование средней сложности,1 зона</t>
+          <t>Программа «Осмотр малыша в 1 месяц»</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:14</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>cosmetologist.ru</t>
+          <t>c9m.ru</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>4200</v>
+        <v>15680</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>LPG- массаж по телу, 40 мин</t>
+          <t>Программа «Я иду в детский сад! Я иду в школу!»</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:14</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>cosmetologist.ru</t>
+          <t>c9m.ru</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>2500</v>
+        <v>19280</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>LPG- массаж по телу, 20 мин</t>
+          <t>Программа обследования для женщин, узнавших о беременности</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:14</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>cosmetologist.ru</t>
+          <t>c9m.ru</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>5500</v>
+        <v>24130</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>LPG- массаж по телу, дополнительное время, 20 мин</t>
+          <t>Программа подготовки к беременности для женщин</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:14</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>cosmetologist.ru</t>
+          <t>c9m.ru</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>5000</v>
+        <v>5070</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>RF - лифтинг тела, 80 мин (3-MAX)</t>
+          <t>Программа обследования партнеров будущих мам</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:14</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>cosmetologist.ru</t>
+          <t>c9m.ru</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>3700</v>
+        <v>17800</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>RF - лифтинг тела, 50 мин (3-MAX)</t>
+          <t>Программа обследования беременных женщин специалистами</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:14</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ostaclinic.ru</t>
+          <t>rmc-clinic.ru</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>2300</v>
+        <v>3000</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Приём (осмотр, консультация) врача-невролога первичный (В01.023.001)</t>
+          <t>Введение внутриматочной спирали</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:7</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ostaclinic.ru</t>
+          <t>rmc-clinic.ru</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>2000</v>
+        <v>9370</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Приём (осмотр, консультация) врача-невролога повторный (В01.023.002)</t>
+          <t>Введение, извлечение влагалищного поддерживающего кольца (пессария)</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:7</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ostaclinic.ru</t>
+          <t>rmc-clinic.ru</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>3700</v>
+        <v>400</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Консультация ведущего специалиста (В01.022.001)</t>
+          <t>Определение концентрации водородных ионов (pH) отделяемого слизистой оболочки влагалища (кольпотест)</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:7</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ostaclinic.ru</t>
+          <t>rmc-clinic.ru</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>2300</v>
+        <v>200</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Приём (осмотр, консультация) врача-рефлексотерапевта первичный (В01.041.001)</t>
+          <t>Получение материала гинекологом для нескольких исследований в одно посещение</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:7</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ostaclinic.ru</t>
+          <t>rmc-clinic.ru</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Приём (осмотр, консультация) аллерголога-иммунолога, д.м.н., профессора (В01.002.001)</t>
+          <t>Получение соскоба с шейки матки (онкоцитология)</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:7</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ostaclinic.ru</t>
+          <t>rmc-clinic.ru</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>2300</v>
+        <v>3000</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Приём (осмотр, консультация) врача-терапевта первичный (В01.047.001)</t>
+          <t>Удаление внутриматочной спирали</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:7</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ostaclinic.ru</t>
+          <t>rmc-clinic.ru</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Приём (осмотр, консультация) врача-терапевта повторный (В01.047.002)</t>
+          <t>Удаление инородного тела из влагалища</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:7</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ostaclinic.ru</t>
+          <t>rmc-clinic.ru</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>2300</v>
+        <v>2000</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Приём (осмотр, консультация) врача-кардиолога (В01.015.001 )</t>
+          <t>Биопсия вульвы на гистологическое исследование</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>таблица</t>
+          <t>паттерн:2125</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>kdmcenter.ru</t>
+          <t>medprak.ru</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Стаж - 9 лет Осипов Дмитрий Александрович Врач-терапевт, врач-психиатр-нарколог, врач общей практики, автор научных стат</t>
+          <t>Прием (осмотр, консультация) врача-онколога повторный</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>паттерн:5</t>
+          <t>паттерн:179</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>kdmcenter.ru</t>
+          <t>medprak.ru</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Стаж - 26 лет Акрам Навид Врач функциональной и ультразвуковой диагностики Врач ультразвуковой диагностики и кардиолог А</t>
+          <t>Прием (осмотр, консультация) врача-хирурга повторный</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>паттерн:4</t>
+          <t>паттерн:179</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>kdmcenter.ru</t>
+          <t>medprak.ru</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>4500</v>
+        <v>2200</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Стаж - 9 лет Осипов Дмитрий Александрович Врач-терапевт, врач-психиатр-нарколог, врач общей практики, автор научных стат</t>
+          <t>Прием (осмотр, консультация) врача-онколога первичный</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>паттерн:7</t>
+          <t>паттерн:179</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>kdmcenter.ru</t>
+          <t>medprak.ru</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>3000</v>
+        <v>2200</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Стаж - 37 лет Фатенкова Светлана Васильевна Врач функциональной и ультразвуковой диагностики, врач-терапевт, стаж работы</t>
+          <t>Прием (осмотр, консультация) врача-хирурга первичный</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>паттерн:8</t>
+          <t>паттерн:179</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>kdmcenter.ru</t>
+          <t>medprak.ru</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>/ Главная Кодирование от алкогольной зависимости Услуги Кодирование /</t>
+          <t>Вскрытие гематом</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>паттерн:5</t>
+          <t>паттерн:179</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>kdmcenter.ru</t>
+          <t>medprak.ru</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>650</v>
+        <v>1500</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Антитела к Вирусу кори IgG (кровь)</t>
+          <t>Вскрытие ограниченного гнойного процесса (панариций 2-х фаланг и более)</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>паттерн:100</t>
+          <t>паттерн:179</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>kdmcenter.ru</t>
+          <t>medprak.ru</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>3500</v>
+        <v>1100</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Первичная консультация кандидата медицинских наук</t>
+          <t>Лечение эпикондилита,пяточной шпоры</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>паттерн:100</t>
+          <t>паттерн:179</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>kdmcenter.ru</t>
+          <t>medprak.ru</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>6000</v>
+        <v>1000</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Первичная консультация доктора медицинских наук, профессора</t>
+          <t>Удаление инородного тела из слухового отверстия</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>паттерн:100</t>
+          <t>паттерн:179</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>centrcosmet.ru</t>
+          <t>chechina-clinic.ru</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>7700</v>
+        <v>1000</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Комплексный профилактический скрининг новообразований кожи на аппарате РДС</t>
+          <t>Консультация врача-косметолога *при выполнении любой процедуры в день первичного приема врача-косметолога, на консультац</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>паттерн:20</t>
+          <t>паттерн:4</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>centrcosmet.ru</t>
+          <t>chechina-clinic.ru</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>3300</v>
+        <v>1000</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Скрининг новообразований (до 3х шт) на аппарате РДС</t>
+          <t>Первичная консультация врача-дерматовенеролога</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>паттерн:20</t>
+          <t>паттерн:4</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>centrcosmet.ru</t>
+          <t>chechina-clinic.ru</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>1700</v>
+        <v>500</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Прием(осмотр, консультация) врача ХИРУРГА ( )</t>
+          <t>Повторная консультация врача-дерматовенеролога (повторный в течении 3 месяцев)</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>паттерн:20</t>
+          <t>паттерн:4</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>centrcosmet.ru</t>
+          <t>chechina-clinic.ru</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Прием(осмотр, консультация) врача ТРИХОЛОГА</t>
+          <t>Аппаратная диагностика кожи лица системой Observ 520X</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>паттерн:20</t>
+          <t>паттерн:4</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>centrcosmet.ru</t>
+          <t>chechina-clinic.ru</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Прием(осмотр, консультация) врача ОНКОЛОГА</t>
+          <t>HydraFacial (ХайдраФешл)</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>паттерн:20</t>
+          <t>паттерн:142</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>centrcosmet.ru</t>
+          <t>chechina-clinic.ru</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>1100</v>
+        <v>3500</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Прием(осмотр, консультация) врача КОСМЕТОЛОГА, ДЕРМАТОВЕНЕРОЛОГА</t>
+          <t>HYDRAFACIAL (Хайдрафешл) пилинг "GlyPeel"</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>паттерн:20</t>
+          <t>паттерн:142</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>centrcosmet.ru</t>
+          <t>chechina-clinic.ru</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -47581,352 +47581,352 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Прием(осмотр, консультация) врача ДЕРМАТОВЕНЕРОЛОГА (профессор )</t>
+          <t>HYDRAFACIAL (Хайдрафешл) пилинг "AlmPeel"</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>паттерн:20</t>
+          <t>паттерн:142</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>centrcosmet.ru</t>
+          <t>chechina-clinic.ru</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>2500</v>
+        <v>5000</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Прием(осмотр, консультация) врача ГОМЕОПАТА (профессор )</t>
+          <t>Фотодинамическая терапия HELEO4 (AntiAcne)</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>паттерн:20</t>
+          <t>паттерн:142</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>perm.varikozanet.info</t>
+          <t>signal-clinic.ru</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>300</v>
+        <v>1600</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Подкожная инъекция без учета стоимости препарата</t>
+          <t>II,III (1.)</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>паттерн:54</t>
+          <t>таблица</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>perm.varikozanet.info</t>
+          <t>signal-clinic.ru</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>300</v>
+        <v>1700</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Внутримышечная инъекция без учета стоимости препарата</t>
+          <t>II,III (1.)</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>паттерн:54</t>
+          <t>таблица</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>perm.varikozanet.info</t>
+          <t>signal-clinic.ru</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>400</v>
+        <v>1800</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Внутривенная инъекция без учета стоимости препарата</t>
+          <t>II,III - (1.)</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>паттерн:54</t>
+          <t>таблица</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>perm.varikozanet.info</t>
+          <t>signal-clinic.ru</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>650</v>
+        <v>170</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Внутривенная инфузия без учета стоимости препарата</t>
+          <t>( Gluma)</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>паттерн:54</t>
+          <t>таблица</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>perm.varikozanet.info</t>
+          <t>signal-clinic.ru</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Введение каждого последующего флакона при внутривенной инфузии без учета стоимости препарата</t>
+          <t>( AirFlow)</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>паттерн:54</t>
+          <t>таблица</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>perm.varikozanet.info</t>
+          <t>signal-clinic.ru</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Инъекция препарата Клексан</t>
+          <t>Прием (осмотр, консультация) врача-терапевта</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>паттерн:54</t>
+          <t>таблица</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>perm.varikozanet.info</t>
+          <t>signal-clinic.ru</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Первичная хирургическая обработка раны до 3 см</t>
+          <t>Прием (осмотр, консультация) врача-акушера-гинеколога</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>паттерн:54</t>
+          <t>таблица</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>perm.varikozanet.info</t>
+          <t>signal-clinic.ru</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Первичная хирургическая обработка раны более 3 см</t>
+          <t>Прием (осмотр, консультация) врача-невролога</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>паттерн:54</t>
+          <t>таблица</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>dagdiag.ru</t>
+          <t>clinicanakirenskogo.ru</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>2496</v>
+        <v>4000</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>РАБОТНИКИ ЖКХ (ПЕРИОДИЧЕСКИЕ) МУЖЧИНЫ</t>
+          <t>Аспирационная биопсия эндометрия Пайпель-тестом</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>паттерн:498</t>
+          <t>таблица</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>dagdiag.ru</t>
+          <t>clinicanakirenskogo.ru</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>3642</v>
+        <v>2500</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>РАБОТНИКИ ЖКХ (ПЕРИОДИЧЕСКИЕ) ЖЕНЩИНЫ ДО 40</t>
+          <t>Введение ВМС</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>паттерн:498</t>
+          <t>таблица</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>dagdiag.ru</t>
+          <t>clinicanakirenskogo.ru</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>4061</v>
+        <v>5000</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>РАБОТНИКИ ЖКХ (ПЕРИОДИЧЕСКИЕ) ЖЕНЩИНЫ 40+</t>
+          <t>Введение/удаление подкожного контрацептива «Импланон»</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>паттерн:498</t>
+          <t>таблица</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>dagdiag.ru</t>
+          <t>clinicanakirenskogo.ru</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>2496</v>
+        <v>3000</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>РАБОТНИКИ ЖКХ (ПРЕДВАРИТЕЛЬНЫЕ) МУЖЧИНЫ</t>
+          <t>Выскабливание цервикального канала</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>паттерн:498</t>
+          <t>таблица</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>dagdiag.ru</t>
+          <t>clinicanakirenskogo.ru</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>3642</v>
+        <v>2500</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>РАБОТНИКИ ЖКХ (ПРЕДВАРИТЕЛЬНЫЕ) ЖЕНЩИНЫ ДО 40</t>
+          <t>Гистологическое исследование</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>паттерн:498</t>
+          <t>таблица</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>dagdiag.ru</t>
+          <t>clinicanakirenskogo.ru</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>4061</v>
+        <v>500</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>РАБОТНИКИ ЖКХ (ПРЕДВАРИТЕЛЬНЫЕ) ЖЕНЩИНЫ 40+</t>
+          <t>Извлечение влагалищного поддерживающего кольца (пессария)/ инородного тела</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>паттерн:498</t>
+          <t>таблица</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>dagdiag.ru</t>
+          <t>clinicanakirenskogo.ru</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>2496</v>
+        <v>500</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>РАБОТНИКИ ПИЩЕВОЙ ПРОМЫШЛЕННОСТИ И ПИЩЕТОРГА (ПЕРИОДИЧЕСКИЕ) МУЖЧИНЫ</t>
+          <t>Интерпретация лабораторных исследований</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>паттерн:498</t>
+          <t>таблица</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>dagdiag.ru</t>
+          <t>clinicanakirenskogo.ru</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>3642</v>
+        <v>2000</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>РАБОТНИКИ ПИЩЕВОЙ ПРОМЫШЛЕННОСТИ И ПИЩЕТОРГА (ПЕРИОДИЧЕСКИЕ) ЖЕНЩИНЫ ДО 40</t>
+          <t>Кольпоскопия первичная на цифровом кольпоскопе SLC-2000</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>паттерн:498</t>
+          <t>таблица</t>
         </is>
       </c>
     </row>
